--- a/eflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Medication.xlsx
+++ b/eflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Medication.xlsx
@@ -7171,7 +7171,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
